--- a/Docs/UserSurveyData.xlsx
+++ b/Docs/UserSurveyData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7305" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7305"/>
   </bookViews>
   <sheets>
     <sheet name="Response Template" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="409">
   <si>
     <t>respondent_id</t>
   </si>
@@ -659,13 +659,601 @@
   </si>
   <si>
     <t>monthly_want_to_pay_usd_code</t>
+  </si>
+  <si>
+    <t>Mia Thompson</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>university_student</t>
+  </si>
+  <si>
+    <t>Build confidence and manage study-related stress.</t>
+  </si>
+  <si>
+    <t>Music helps me reset quickly when assignments and social pressures feel overwhelming.</t>
+  </si>
+  <si>
+    <t>Regular playlists help me regulate mood and maintain routines.</t>
+  </si>
+  <si>
+    <t>I use upbeat music for exercise, ambient music for study and softer tracks at night.</t>
+  </si>
+  <si>
+    <t>Talking things through usually helps me identify what is actually bothering me.</t>
+  </si>
+  <si>
+    <t>Friends are not always available when stress peaks late at night.</t>
+  </si>
+  <si>
+    <t>A supportive conversation followed by the right music could help me act on insights.</t>
+  </si>
+  <si>
+    <t>I would be comfortable if privacy settings were clear and I could delete my data.</t>
+  </si>
+  <si>
+    <t>I already use digital wellbeing tools and would try one that combines support with music.</t>
+  </si>
+  <si>
+    <t>few_times_week</t>
+  </si>
+  <si>
+    <t>10_to_30_minutes</t>
+  </si>
+  <si>
+    <t>hybrid_adaptive</t>
+  </si>
+  <si>
+    <t>free_trial_subscription</t>
+  </si>
+  <si>
+    <t>under_10</t>
+  </si>
+  <si>
+    <t>The service should feel warm and practical rather than clinical.</t>
+  </si>
+  <si>
+    <t>Liam O'Connor</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
+  </si>
+  <si>
+    <t>early_career_professional</t>
+  </si>
+  <si>
+    <t>Create better work-life boundaries and sleep more consistently.</t>
+  </si>
+  <si>
+    <t>Music helps me switch out of work mode after demanding days.</t>
+  </si>
+  <si>
+    <t>It supports exercise, focus and decompression, which improves my overall balance.</t>
+  </si>
+  <si>
+    <t>My work, gym and weekend playlists are completely different.</t>
+  </si>
+  <si>
+    <t>A structured conversation can stop me from carrying problems around in my head.</t>
+  </si>
+  <si>
+    <t>I have people to talk to, but I do not always want to burden them.</t>
+  </si>
+  <si>
+    <t>Conversation could identify the need and music could reinforce the desired state.</t>
+  </si>
+  <si>
+    <t>I would need strong privacy controls and transparent explanations of how recommendations are made.</t>
+  </si>
+  <si>
+    <t>I would use it if it saved time and integrated with my existing music service.</t>
+  </si>
+  <si>
+    <t>weekly</t>
+  </si>
+  <si>
+    <t>5_to_10_minutes</t>
+  </si>
+  <si>
+    <t>gradual_learning</t>
+  </si>
+  <si>
+    <t>monthly_subscription</t>
+  </si>
+  <si>
+    <t>10_to_20</t>
+  </si>
+  <si>
+    <t>Integration with Spotify and calendar-based routines would increase usefulness.</t>
+  </si>
+  <si>
+    <t>Aarav Mehta</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Reduce anxiety about career progression and improve daily focus.</t>
+  </si>
+  <si>
+    <t>Music is my fastest way to calm down and regain concentration.</t>
+  </si>
+  <si>
+    <t>It has been part of my study and work routines for years.</t>
+  </si>
+  <si>
+    <t>Instrumental music helps me code, while energetic music helps during workouts.</t>
+  </si>
+  <si>
+    <t>Questions from another perspective often help me organise my thoughts.</t>
+  </si>
+  <si>
+    <t>I sometimes need support outside the hours when friends and family are free.</t>
+  </si>
+  <si>
+    <t>The conversation could understand the problem and select music for the right emotional direction.</t>
+  </si>
+  <si>
+    <t>I am comfortable with AI if data use is consent-based and clearly documented.</t>
+  </si>
+  <si>
+    <t>Personalised support that fits into short breaks would be valuable.</t>
+  </si>
+  <si>
+    <t>daily_or_more</t>
+  </si>
+  <si>
+    <t>Support for Indian languages and regional music would be important.</t>
+  </si>
+  <si>
+    <t>Sophie Chen</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>senior_professional</t>
+  </si>
+  <si>
+    <t>Protect personal time and maintain emotional energy while leading a team.</t>
+  </si>
+  <si>
+    <t>Music gives me a reliable transition between professional and family responsibilities.</t>
+  </si>
+  <si>
+    <t>It helps sustain calm routines and keeps me connected to positive memories.</t>
+  </si>
+  <si>
+    <t>I prefer classical or acoustic music for reflection and upbeat pop for commuting.</t>
+  </si>
+  <si>
+    <t>Meaningful dialogue helps me separate immediate pressure from longer-term priorities.</t>
+  </si>
+  <si>
+    <t>I have a support network, but discretion and convenience can matter.</t>
+  </si>
+  <si>
+    <t>Used thoughtfully, music could deepen or stabilise the outcome of a reflective conversation.</t>
+  </si>
+  <si>
+    <t>I would require credible security, minimal data collection and control over personalisation.</t>
+  </si>
+  <si>
+    <t>I would use it occasionally if the experience were mature and not intrusive.</t>
+  </si>
+  <si>
+    <t>occasionally</t>
+  </si>
+  <si>
+    <t>upfront_preferences</t>
+  </si>
+  <si>
+    <t>The tone should be respectful, calm and suitable for busy professionals.</t>
+  </si>
+  <si>
+    <t>Jack Wilson</t>
+  </si>
+  <si>
+    <t>NZ</t>
+  </si>
+  <si>
+    <t>Auckland</t>
+  </si>
+  <si>
+    <t>high_school_student</t>
+  </si>
+  <si>
+    <t>Feel less stressed about exams and decide what to study after school.</t>
+  </si>
+  <si>
+    <t>Music distracts me from overthinking and makes study breaks feel better.</t>
+  </si>
+  <si>
+    <t>It helps me keep a positive mood, although it can also become a distraction.</t>
+  </si>
+  <si>
+    <t>I use lo-fi for homework and louder music when gaming or exercising.</t>
+  </si>
+  <si>
+    <t>It helps when someone asks questions instead of immediately giving advice.</t>
+  </si>
+  <si>
+    <t>I do not always feel comfortable discussing everything with adults or friends.</t>
+  </si>
+  <si>
+    <t>Music could make an AI conversation feel less awkward and more supportive.</t>
+  </si>
+  <si>
+    <t>I would use it if it was private and did not share information with school or advertisers.</t>
+  </si>
+  <si>
+    <t>I would probably use it during exams or when I cannot sleep.</t>
+  </si>
+  <si>
+    <t>free_only</t>
+  </si>
+  <si>
+    <t>It should have age-appropriate safety features without feeling childish.</t>
+  </si>
+  <si>
+    <t>Olivia Bennett</t>
+  </si>
+  <si>
+    <t>Brisbane</t>
+  </si>
+  <si>
+    <t>parent_caregiver</t>
+  </si>
+  <si>
+    <t>Make more time for self-care while balancing work and parenting.</t>
+  </si>
+  <si>
+    <t>Music can lift the atmosphere at home and give me a moment to breathe.</t>
+  </si>
+  <si>
+    <t>Shared music and personal playlists both help maintain connection and resilience.</t>
+  </si>
+  <si>
+    <t>Family music, exercise music and quiet evening music serve different purposes.</t>
+  </si>
+  <si>
+    <t>Speaking openly helps me notice when I have neglected my own needs.</t>
+  </si>
+  <si>
+    <t>My available time rarely matches other people's availability.</t>
+  </si>
+  <si>
+    <t>A brief conversation plus a tailored song could provide support without demanding much time.</t>
+  </si>
+  <si>
+    <t>I would use it with strong privacy, clear boundaries and crisis escalation guidance.</t>
+  </si>
+  <si>
+    <t>Short, flexible interactions would fit around family responsibilities.</t>
+  </si>
+  <si>
+    <t>under_5_minutes</t>
+  </si>
+  <si>
+    <t>Hands-free use while walking or doing chores would be helpful.</t>
+  </si>
+  <si>
+    <t>Noah Williams</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Seattle</t>
+  </si>
+  <si>
+    <t>Improve health habits and reduce the stress of a demanding leadership role.</t>
+  </si>
+  <si>
+    <t>Music helps, but exercise and talking with my partner are usually more effective.</t>
+  </si>
+  <si>
+    <t>Music supports routines and provides enjoyment, especially during travel and exercise.</t>
+  </si>
+  <si>
+    <t>I choose different genres for workouts, driving and quiet evenings.</t>
+  </si>
+  <si>
+    <t>Good conversations expose blind spots and help me make better decisions.</t>
+  </si>
+  <si>
+    <t>I usually have someone available, so constant access is not a major need.</t>
+  </si>
+  <si>
+    <t>The combination could work, but it would need to avoid feeling gimmicky.</t>
+  </si>
+  <si>
+    <t>I am cautious about storing sensitive conversations with a commercial AI service.</t>
+  </si>
+  <si>
+    <t>I might test it, but regular use would depend on clear evidence of benefit.</t>
+  </si>
+  <si>
+    <t>difficult_periods_only</t>
+  </si>
+  <si>
+    <t>mostly_unchanged</t>
+  </si>
+  <si>
+    <t>pay_per_use</t>
+  </si>
+  <si>
+    <t>Independent evidence, transparent limitations and local data storage would matter.</t>
+  </si>
+  <si>
+    <t>Amelia Clarke</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>retired</t>
+  </si>
+  <si>
+    <t>Stay socially connected and keep a positive daily routine.</t>
+  </si>
+  <si>
+    <t>Familiar songs bring comfort and remind me of important people and times.</t>
+  </si>
+  <si>
+    <t>Music has supported me through bereavement, change and many stages of life.</t>
+  </si>
+  <si>
+    <t>I choose calming classical music when anxious and lively older songs when I need energy.</t>
+  </si>
+  <si>
+    <t>A thoughtful conversation often makes worries feel more manageable.</t>
+  </si>
+  <si>
+    <t>Some evenings feel lonely even though I have family and friends.</t>
+  </si>
+  <si>
+    <t>Conversation and familiar music together could offer companionship and reassurance.</t>
+  </si>
+  <si>
+    <t>I would need simple controls, clear privacy explanations and an easy way to get human help.</t>
+  </si>
+  <si>
+    <t>I would use it if it were easy to operate by voice.</t>
+  </si>
+  <si>
+    <t>Large text, voice control and straightforward language would make it accessible.</t>
+  </si>
+  <si>
+    <t>Alex Morgan</t>
+  </si>
+  <si>
+    <t>non_binary</t>
+  </si>
+  <si>
+    <t>Adelaide</t>
+  </si>
+  <si>
+    <t>entrepreneur</t>
+  </si>
+  <si>
+    <t>During creative work and journaling</t>
+  </si>
+  <si>
+    <t>Maintain emotional balance while growing a small creative business.</t>
+  </si>
+  <si>
+    <t>Music helps me process emotions without needing to explain them immediately.</t>
+  </si>
+  <si>
+    <t>It supports identity, creativity and recovery from stressful periods.</t>
+  </si>
+  <si>
+    <t>My choices vary with creative work, social energy, anxiety and the need to rest.</t>
+  </si>
+  <si>
+    <t>Reflective conversations help turn vague feelings into decisions and boundaries.</t>
+  </si>
+  <si>
+    <t>Entrepreneurship can be isolating and support is not always available when needed.</t>
+  </si>
+  <si>
+    <t>The combination could make emotional support more personalised and embodied.</t>
+  </si>
+  <si>
+    <t>I would trust it with granular consent, inclusive language and the ability to correct what it learns.</t>
+  </si>
+  <si>
+    <t>I would use it frequently for emotional regulation and creative focus.</t>
+  </si>
+  <si>
+    <t>Uses inclusive language and remembers preferred identity terms</t>
+  </si>
+  <si>
+    <t>Personalisation should include identity, sensory preferences and changing energy levels.</t>
+  </si>
+  <si>
+    <t>Hana Petrović</t>
+  </si>
+  <si>
+    <t>prefer_not_say</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Split</t>
+  </si>
+  <si>
+    <t>Remain independent and feel less isolated during quiet days.</t>
+  </si>
+  <si>
+    <t>Traditional songs and radio programmes provide comfort and familiarity.</t>
+  </si>
+  <si>
+    <t>Music has helped preserve memories and connection with family traditions.</t>
+  </si>
+  <si>
+    <t>I mostly prefer familiar music, though I choose quieter songs when tired.</t>
+  </si>
+  <si>
+    <t>A patient listener can help me express concerns I might otherwise keep to myself.</t>
+  </si>
+  <si>
+    <t>Family members live in different places and are not always available.</t>
+  </si>
+  <si>
+    <t>A friendly voice with familiar music could make the home feel less quiet.</t>
+  </si>
+  <si>
+    <t>I would be cautious and would need help from family to understand privacy and settings.</t>
+  </si>
+  <si>
+    <t>I might use it if it worked by voice and required very little setup.</t>
+  </si>
+  <si>
+    <t>as_long_as_needed</t>
+  </si>
+  <si>
+    <t>Difficulty learning to use a new device or service</t>
+  </si>
+  <si>
+    <t>It should work in Croatian and allow a trusted family member to assist with setup.</t>
+  </si>
+  <si>
+    <t>ai.persona11@example.com</t>
+  </si>
+  <si>
+    <t>Alex AI</t>
+  </si>
+  <si>
+    <t>free_trial_then_paid_subscription</t>
+  </si>
+  <si>
+    <t>less_than_usd10</t>
+  </si>
+  <si>
+    <t>ai.persona12@example.com</t>
+  </si>
+  <si>
+    <t>Emma AI</t>
+  </si>
+  <si>
+    <t>ai.persona13@example.com</t>
+  </si>
+  <si>
+    <t>Liam AI</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>ai.persona14@example.com</t>
+  </si>
+  <si>
+    <t>Olivia AI</t>
+  </si>
+  <si>
+    <t>ai.persona15@example.com</t>
+  </si>
+  <si>
+    <t>Noah AI</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>ai.persona16@example.com</t>
+  </si>
+  <si>
+    <t>Mia AI</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>ai.persona17@example.com</t>
+  </si>
+  <si>
+    <t>Ethan AI</t>
+  </si>
+  <si>
+    <t>ai.persona18@example.com</t>
+  </si>
+  <si>
+    <t>Chloe AI</t>
+  </si>
+  <si>
+    <t>ai.persona19@example.com</t>
+  </si>
+  <si>
+    <t>Lucas AI</t>
+  </si>
+  <si>
+    <t>ai.persona20@example.com</t>
+  </si>
+  <si>
+    <t>Grace AI</t>
+  </si>
+  <si>
+    <t>ai.persona1@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona2@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona3@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona4@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona5@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona6@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona7@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona8@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona9@example.com</t>
+  </si>
+  <si>
+    <t>ai.persona10@example.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -674,6 +1262,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -719,10 +1313,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -739,8 +1334,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -905,19 +1505,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CH1"/>
+  <dimension ref="A1:CH21"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.5625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.4375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.3125" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.3125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="30.75" bestFit="1" customWidth="1"/>
@@ -934,26 +1534,26 @@
     <col min="24" max="24" width="21.875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="20.75" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.6875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="25.0625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.3125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="23.4375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="22.4375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="31" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.4375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="38.5625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="22.5625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="28.0625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="34.4375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="27.875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="33.375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="41.6875" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="43.5" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="32.5625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="38.125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="47.4375" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="26.25" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="31.6875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="42.1875" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="27.9375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="34.75" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="22.4375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="31.0625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.6875" bestFit="1" customWidth="1"/>
@@ -971,7 +1571,7 @@
     <col min="61" max="61" width="30" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="29.8125" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="20.6875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="25" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="28.8125" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="30.3125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="29.6875" bestFit="1" customWidth="1"/>
     <col min="67" max="67" width="26.25" bestFit="1" customWidth="1"/>
@@ -990,10 +1590,10 @@
     <col min="80" max="80" width="20.0625" bestFit="1" customWidth="1"/>
     <col min="81" max="81" width="13.5625" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="18.0625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="21.1875" bestFit="1" customWidth="1"/>
     <col min="84" max="84" width="18.6875" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="29.75" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="24" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="34.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:86" ht="27.75">
@@ -1256,7 +1856,3807 @@
         <v>84</v>
       </c>
     </row>
+    <row r="2" spans="1:86" ht="40.5">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" s="6">
+        <v>22</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6">
+        <v>5</v>
+      </c>
+      <c r="M2" s="6">
+        <v>5</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1</v>
+      </c>
+      <c r="O2" s="6">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6">
+        <v>1</v>
+      </c>
+      <c r="S2" s="6">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6">
+        <v>1</v>
+      </c>
+      <c r="V2" s="6">
+        <v>1</v>
+      </c>
+      <c r="W2" s="6">
+        <v>1</v>
+      </c>
+      <c r="X2" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC2" s="6">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="AG2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AI2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="AM2" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="AO2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP2" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="AQ2" s="6">
+        <v>4</v>
+      </c>
+      <c r="AR2" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AT2" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN2" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="BP2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BS2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV2" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="6">
+        <v>1</v>
+      </c>
+      <c r="BZ2" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA2" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB2" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC2" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CG2" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH2" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:86" ht="40.5">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="6">
+        <v>34</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6">
+        <v>5</v>
+      </c>
+      <c r="M3" s="6">
+        <v>4</v>
+      </c>
+      <c r="N3" s="6">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6">
+        <v>1</v>
+      </c>
+      <c r="P3" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>1</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6">
+        <v>1</v>
+      </c>
+      <c r="V3" s="6">
+        <v>1</v>
+      </c>
+      <c r="W3" s="6">
+        <v>1</v>
+      </c>
+      <c r="X3" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="AC3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="AG3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI3" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="AK3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="AO3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="AQ3" s="6">
+        <v>3</v>
+      </c>
+      <c r="AR3" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AT3" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="AU3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="6"/>
+      <c r="BD3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BG3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="6"/>
+      <c r="BM3" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN3" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="BO3" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="BP3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW3" s="6"/>
+      <c r="BX3" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ3" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA3" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB3" s="6">
+        <v>1</v>
+      </c>
+      <c r="CC3" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD3" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE3" s="6"/>
+      <c r="CF3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="CG3" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="CH3" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:86" ht="27">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4" s="6">
+        <v>28</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6">
+        <v>5</v>
+      </c>
+      <c r="M4" s="6">
+        <v>5</v>
+      </c>
+      <c r="N4" s="6">
+        <v>1</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>1</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6">
+        <v>1</v>
+      </c>
+      <c r="V4" s="6">
+        <v>1</v>
+      </c>
+      <c r="W4" s="6">
+        <v>1</v>
+      </c>
+      <c r="X4" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AM4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="AO4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="AQ4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="AS4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="AU4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BG4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="BN4" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="BO4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="BP4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BS4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV4" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY4" s="6">
+        <v>1</v>
+      </c>
+      <c r="BZ4" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA4" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB4" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC4" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD4" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CG4" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH4" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:86" ht="40.5">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6">
+        <v>4</v>
+      </c>
+      <c r="M5" s="6">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6">
+        <v>1</v>
+      </c>
+      <c r="O5" s="6">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>1</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6">
+        <v>1</v>
+      </c>
+      <c r="V5" s="6">
+        <v>0</v>
+      </c>
+      <c r="W5" s="6">
+        <v>0</v>
+      </c>
+      <c r="X5" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="AK5" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="AM5" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="AO5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AP5" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="AQ5" s="6">
+        <v>3</v>
+      </c>
+      <c r="AR5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="AS5" s="6">
+        <v>3</v>
+      </c>
+      <c r="AT5" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="AU5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="6"/>
+      <c r="BD5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="6"/>
+      <c r="BM5" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="BN5" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO5" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="BP5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BR5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW5" s="6"/>
+      <c r="BX5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY5" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ5" s="6">
+        <v>1</v>
+      </c>
+      <c r="CA5" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB5" s="6">
+        <v>1</v>
+      </c>
+      <c r="CC5" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD5" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE5" s="6"/>
+      <c r="CF5" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="CG5" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="CH5" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:86" ht="27">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="6">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6">
+        <v>5</v>
+      </c>
+      <c r="M6" s="6">
+        <v>5</v>
+      </c>
+      <c r="N6" s="6">
+        <v>1</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6">
+        <v>1</v>
+      </c>
+      <c r="V6" s="6">
+        <v>1</v>
+      </c>
+      <c r="W6" s="6">
+        <v>1</v>
+      </c>
+      <c r="X6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AP6" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AR6" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AT6" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AU6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="6"/>
+      <c r="BD6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="6"/>
+      <c r="BM6" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN6" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="BO6" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="BP6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BR6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BS6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV6" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW6" s="6"/>
+      <c r="BX6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BZ6" s="6">
+        <v>1</v>
+      </c>
+      <c r="CA6" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB6" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC6" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD6" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE6" s="6"/>
+      <c r="CF6" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG6" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="CH6" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:86" ht="40.5">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="6">
+        <v>39</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6">
+        <v>4</v>
+      </c>
+      <c r="M7" s="6">
+        <v>4</v>
+      </c>
+      <c r="N7" s="6">
+        <v>1</v>
+      </c>
+      <c r="O7" s="6">
+        <v>1</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6">
+        <v>1</v>
+      </c>
+      <c r="V7" s="6">
+        <v>1</v>
+      </c>
+      <c r="W7" s="6">
+        <v>0</v>
+      </c>
+      <c r="X7" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="AG7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL7" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="AM7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="AO7" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP7" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AQ7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AR7" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="AS7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="AU7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="6"/>
+      <c r="BD7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL7" s="6"/>
+      <c r="BM7" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN7" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="BO7" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="BP7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BS7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV7" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW7" s="6"/>
+      <c r="BX7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY7" s="6">
+        <v>1</v>
+      </c>
+      <c r="BZ7" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA7" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB7" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC7" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD7" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE7" s="6"/>
+      <c r="CF7" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CG7" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH7" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:86" ht="40.5">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="6">
+        <v>53</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6">
+        <v>4</v>
+      </c>
+      <c r="M8" s="6">
+        <v>3</v>
+      </c>
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6">
+        <v>1</v>
+      </c>
+      <c r="P8" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1</v>
+      </c>
+      <c r="R8" s="6">
+        <v>1</v>
+      </c>
+      <c r="S8" s="6">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6">
+        <v>1</v>
+      </c>
+      <c r="V8" s="6">
+        <v>1</v>
+      </c>
+      <c r="W8" s="6">
+        <v>0</v>
+      </c>
+      <c r="X8" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE8" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AG8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AK8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="AM8" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO8" s="6">
+        <v>3</v>
+      </c>
+      <c r="AP8" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AQ8" s="6">
+        <v>2</v>
+      </c>
+      <c r="AR8" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="AS8" s="6">
+        <v>2</v>
+      </c>
+      <c r="AT8" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AU8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="6"/>
+      <c r="BD8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BG8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="6"/>
+      <c r="BM8" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="BN8" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO8" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BQ8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BU8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW8" s="6"/>
+      <c r="BX8" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ8" s="6">
+        <v>1</v>
+      </c>
+      <c r="CA8" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB8" s="6">
+        <v>1</v>
+      </c>
+      <c r="CC8" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD8" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE8" s="6"/>
+      <c r="CF8" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="CG8" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH8" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:86" ht="40.5">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="6">
+        <v>67</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6">
+        <v>3</v>
+      </c>
+      <c r="M9" s="6">
+        <v>4</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>1</v>
+      </c>
+      <c r="P9" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1</v>
+      </c>
+      <c r="R9" s="6">
+        <v>1</v>
+      </c>
+      <c r="S9" s="6">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6">
+        <v>1</v>
+      </c>
+      <c r="V9" s="6">
+        <v>0</v>
+      </c>
+      <c r="W9" s="6">
+        <v>0</v>
+      </c>
+      <c r="X9" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AG9" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="AK9" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="AM9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="AO9" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AQ9" s="6">
+        <v>3</v>
+      </c>
+      <c r="AR9" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AS9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AT9" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="AU9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="6"/>
+      <c r="BD9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="6"/>
+      <c r="BM9" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN9" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO9" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="BP9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW9" s="6"/>
+      <c r="BX9" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY9" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ9" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA9" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB9" s="6">
+        <v>1</v>
+      </c>
+      <c r="CC9" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD9" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE9" s="6"/>
+      <c r="CF9" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CG9" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CH9" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:86" ht="40.5">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E10" s="6">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6">
+        <v>5</v>
+      </c>
+      <c r="M10" s="6">
+        <v>5</v>
+      </c>
+      <c r="N10" s="6">
+        <v>1</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6">
+        <v>1</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6">
+        <v>1</v>
+      </c>
+      <c r="V10" s="6">
+        <v>1</v>
+      </c>
+      <c r="W10" s="6">
+        <v>1</v>
+      </c>
+      <c r="X10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>2</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="AG10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="AM10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AO10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="AQ10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AR10" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="AS10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AT10" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AU10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="6"/>
+      <c r="BD10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF10" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BH10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BJ10" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BL10" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="BM10" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="BN10" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO10" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="BP10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BS10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BT10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BV10" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="6"/>
+      <c r="BX10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="6">
+        <v>1</v>
+      </c>
+      <c r="BZ10" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA10" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB10" s="6">
+        <v>0</v>
+      </c>
+      <c r="CC10" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD10" s="6">
+        <v>0</v>
+      </c>
+      <c r="CE10" s="6"/>
+      <c r="CF10" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="CG10" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="CH10" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:86" ht="40.5">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="6">
+        <v>78</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6">
+        <v>2</v>
+      </c>
+      <c r="M11" s="6">
+        <v>3</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <v>1</v>
+      </c>
+      <c r="P11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>1</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6">
+        <v>0</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0</v>
+      </c>
+      <c r="X11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH11" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ11" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL11" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN11" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AP11" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="AQ11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AR11" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="AS11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AT11" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AU11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="6"/>
+      <c r="BD11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BE11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BI11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="6"/>
+      <c r="BM11" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="BN11" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="BO11" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="BP11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BQ11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BR11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BS11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BT11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BU11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BV11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BW11" s="6"/>
+      <c r="BX11" s="6">
+        <v>1</v>
+      </c>
+      <c r="BY11" s="6">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="CA11" s="6">
+        <v>0</v>
+      </c>
+      <c r="CB11" s="6">
+        <v>1</v>
+      </c>
+      <c r="CC11" s="6">
+        <v>0</v>
+      </c>
+      <c r="CD11" s="6">
+        <v>1</v>
+      </c>
+      <c r="CE11" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="CF11" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="CG11" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="CH11" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:86">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" t="s">
+        <v>216</v>
+      </c>
+      <c r="J12" t="s">
+        <v>285</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>5</v>
+      </c>
+      <c r="AD12">
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <v>4</v>
+      </c>
+      <c r="AG12">
+        <v>5</v>
+      </c>
+      <c r="AI12">
+        <v>4</v>
+      </c>
+      <c r="AK12">
+        <v>5</v>
+      </c>
+      <c r="AM12">
+        <v>5</v>
+      </c>
+      <c r="AO12">
+        <v>4</v>
+      </c>
+      <c r="AQ12">
+        <v>3</v>
+      </c>
+      <c r="AS12">
+        <v>3</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>1</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>1</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>1</v>
+      </c>
+      <c r="BX12">
+        <v>1</v>
+      </c>
+      <c r="BY12">
+        <v>1</v>
+      </c>
+      <c r="BZ12">
+        <v>1</v>
+      </c>
+      <c r="CA12">
+        <v>1</v>
+      </c>
+      <c r="CB12">
+        <v>0</v>
+      </c>
+      <c r="CC12">
+        <v>1</v>
+      </c>
+      <c r="CD12">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:86">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>378</v>
+      </c>
+      <c r="D13" t="s">
+        <v>379</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" t="s">
+        <v>216</v>
+      </c>
+      <c r="J13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>4</v>
+      </c>
+      <c r="AD13">
+        <v>3</v>
+      </c>
+      <c r="AE13">
+        <v>5</v>
+      </c>
+      <c r="AG13">
+        <v>5</v>
+      </c>
+      <c r="AI13">
+        <v>5</v>
+      </c>
+      <c r="AK13">
+        <v>3</v>
+      </c>
+      <c r="AM13">
+        <v>5</v>
+      </c>
+      <c r="AO13">
+        <v>4</v>
+      </c>
+      <c r="AQ13">
+        <v>4</v>
+      </c>
+      <c r="AS13">
+        <v>3</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>1</v>
+      </c>
+      <c r="BF13">
+        <v>1</v>
+      </c>
+      <c r="BG13">
+        <v>1</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>1</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>1</v>
+      </c>
+      <c r="CA13">
+        <v>1</v>
+      </c>
+      <c r="CB13">
+        <v>1</v>
+      </c>
+      <c r="CC13">
+        <v>0</v>
+      </c>
+      <c r="CD13">
+        <v>1</v>
+      </c>
+      <c r="CF13" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:86">
+      <c r="A14" s="6">
+        <v>1013</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>380</v>
+      </c>
+      <c r="D14" t="s">
+        <v>381</v>
+      </c>
+      <c r="E14">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>234</v>
+      </c>
+      <c r="G14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I14" t="s">
+        <v>382</v>
+      </c>
+      <c r="J14" t="s">
+        <v>236</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>5</v>
+      </c>
+      <c r="AD14">
+        <v>3</v>
+      </c>
+      <c r="AE14">
+        <v>4</v>
+      </c>
+      <c r="AG14">
+        <v>4</v>
+      </c>
+      <c r="AI14">
+        <v>5</v>
+      </c>
+      <c r="AK14">
+        <v>4</v>
+      </c>
+      <c r="AM14">
+        <v>5</v>
+      </c>
+      <c r="AO14">
+        <v>5</v>
+      </c>
+      <c r="AQ14">
+        <v>5</v>
+      </c>
+      <c r="AS14">
+        <v>4</v>
+      </c>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BE14">
+        <v>1</v>
+      </c>
+      <c r="BF14">
+        <v>1</v>
+      </c>
+      <c r="BG14">
+        <v>1</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>1</v>
+      </c>
+      <c r="BJ14">
+        <v>1</v>
+      </c>
+      <c r="BK14">
+        <v>1</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>1</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14">
+        <v>1</v>
+      </c>
+      <c r="CC14">
+        <v>1</v>
+      </c>
+      <c r="CD14">
+        <v>1</v>
+      </c>
+      <c r="CF14" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG14" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:86">
+      <c r="A15" s="6">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>383</v>
+      </c>
+      <c r="D15" t="s">
+        <v>384</v>
+      </c>
+      <c r="E15">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" t="s">
+        <v>298</v>
+      </c>
+      <c r="J15" t="s">
+        <v>236</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>5</v>
+      </c>
+      <c r="AD15">
+        <v>4</v>
+      </c>
+      <c r="AE15">
+        <v>5</v>
+      </c>
+      <c r="AG15">
+        <v>4</v>
+      </c>
+      <c r="AI15">
+        <v>4</v>
+      </c>
+      <c r="AK15">
+        <v>3</v>
+      </c>
+      <c r="AM15">
+        <v>3</v>
+      </c>
+      <c r="AO15">
+        <v>3</v>
+      </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
+      <c r="AS15">
+        <v>3</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>1</v>
+      </c>
+      <c r="BI15">
+        <v>1</v>
+      </c>
+      <c r="BJ15">
+        <v>1</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>1</v>
+      </c>
+      <c r="BY15">
+        <v>1</v>
+      </c>
+      <c r="BZ15">
+        <v>1</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15">
+        <v>1</v>
+      </c>
+      <c r="CC15">
+        <v>1</v>
+      </c>
+      <c r="CD15">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:86">
+      <c r="A16" s="6">
+        <v>1015</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E16">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" t="s">
+        <v>328</v>
+      </c>
+      <c r="I16" t="s">
+        <v>387</v>
+      </c>
+      <c r="J16" t="s">
+        <v>269</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>3</v>
+      </c>
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>3</v>
+      </c>
+      <c r="AG16">
+        <v>3</v>
+      </c>
+      <c r="AI16">
+        <v>3</v>
+      </c>
+      <c r="AK16">
+        <v>3</v>
+      </c>
+      <c r="AM16">
+        <v>3</v>
+      </c>
+      <c r="AO16">
+        <v>3</v>
+      </c>
+      <c r="AQ16">
+        <v>5</v>
+      </c>
+      <c r="AS16">
+        <v>4</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>1</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>1</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>1</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>1</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>1</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16">
+        <v>1</v>
+      </c>
+      <c r="CC16">
+        <v>0</v>
+      </c>
+      <c r="CD16">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="17" spans="1:85">
+      <c r="A17" s="6">
+        <v>1016</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>388</v>
+      </c>
+      <c r="D17" t="s">
+        <v>389</v>
+      </c>
+      <c r="E17">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" t="s">
+        <v>253</v>
+      </c>
+      <c r="I17" t="s">
+        <v>390</v>
+      </c>
+      <c r="J17" t="s">
+        <v>344</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>4</v>
+      </c>
+      <c r="AD17">
+        <v>4</v>
+      </c>
+      <c r="AE17">
+        <v>3</v>
+      </c>
+      <c r="AG17">
+        <v>5</v>
+      </c>
+      <c r="AI17">
+        <v>5</v>
+      </c>
+      <c r="AK17">
+        <v>3</v>
+      </c>
+      <c r="AM17">
+        <v>4</v>
+      </c>
+      <c r="AO17">
+        <v>4</v>
+      </c>
+      <c r="AQ17">
+        <v>5</v>
+      </c>
+      <c r="AS17">
+        <v>5</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>1</v>
+      </c>
+      <c r="BH17">
+        <v>1</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>1</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>1</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>1</v>
+      </c>
+      <c r="CB17">
+        <v>0</v>
+      </c>
+      <c r="CC17">
+        <v>0</v>
+      </c>
+      <c r="CD17">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:85">
+      <c r="A18" s="6">
+        <v>1017</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>391</v>
+      </c>
+      <c r="D18" t="s">
+        <v>392</v>
+      </c>
+      <c r="E18">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>342</v>
+      </c>
+      <c r="G18" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J18" t="s">
+        <v>299</v>
+      </c>
+      <c r="L18">
+        <v>5</v>
+      </c>
+      <c r="M18">
+        <v>5</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>5</v>
+      </c>
+      <c r="AD18">
+        <v>4</v>
+      </c>
+      <c r="AE18">
+        <v>5</v>
+      </c>
+      <c r="AG18">
+        <v>3</v>
+      </c>
+      <c r="AI18">
+        <v>5</v>
+      </c>
+      <c r="AK18">
+        <v>3</v>
+      </c>
+      <c r="AM18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>3</v>
+      </c>
+      <c r="AS18">
+        <v>5</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BE18">
+        <v>1</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>1</v>
+      </c>
+      <c r="BH18">
+        <v>1</v>
+      </c>
+      <c r="BI18">
+        <v>1</v>
+      </c>
+      <c r="BJ18">
+        <v>1</v>
+      </c>
+      <c r="BK18">
+        <v>1</v>
+      </c>
+      <c r="BX18">
+        <v>1</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>1</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18">
+        <v>1</v>
+      </c>
+      <c r="CC18">
+        <v>0</v>
+      </c>
+      <c r="CD18">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:85">
+      <c r="A19" s="6">
+        <v>1018</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>393</v>
+      </c>
+      <c r="D19" t="s">
+        <v>394</v>
+      </c>
+      <c r="E19">
+        <v>55</v>
+      </c>
+      <c r="F19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I19" t="s">
+        <v>254</v>
+      </c>
+      <c r="J19" t="s">
+        <v>269</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>3</v>
+      </c>
+      <c r="AD19">
+        <v>4</v>
+      </c>
+      <c r="AE19">
+        <v>3</v>
+      </c>
+      <c r="AG19">
+        <v>3</v>
+      </c>
+      <c r="AI19">
+        <v>3</v>
+      </c>
+      <c r="AK19">
+        <v>4</v>
+      </c>
+      <c r="AM19">
+        <v>3</v>
+      </c>
+      <c r="AO19">
+        <v>3</v>
+      </c>
+      <c r="AQ19">
+        <v>4</v>
+      </c>
+      <c r="AS19">
+        <v>5</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BE19">
+        <v>1</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>1</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19">
+        <v>1</v>
+      </c>
+      <c r="CC19">
+        <v>0</v>
+      </c>
+      <c r="CD19">
+        <v>1</v>
+      </c>
+      <c r="CF19" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:85">
+      <c r="A20" s="6">
+        <v>1019</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>395</v>
+      </c>
+      <c r="D20" t="s">
+        <v>396</v>
+      </c>
+      <c r="E20">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" t="s">
+        <v>312</v>
+      </c>
+      <c r="I20" t="s">
+        <v>382</v>
+      </c>
+      <c r="J20" t="s">
+        <v>330</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>4</v>
+      </c>
+      <c r="AD20">
+        <v>4</v>
+      </c>
+      <c r="AE20">
+        <v>3</v>
+      </c>
+      <c r="AG20">
+        <v>5</v>
+      </c>
+      <c r="AI20">
+        <v>4</v>
+      </c>
+      <c r="AK20">
+        <v>5</v>
+      </c>
+      <c r="AM20">
+        <v>4</v>
+      </c>
+      <c r="AO20">
+        <v>3</v>
+      </c>
+      <c r="AQ20">
+        <v>5</v>
+      </c>
+      <c r="AS20">
+        <v>3</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>1</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>1</v>
+      </c>
+      <c r="BJ20">
+        <v>1</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>1</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>1</v>
+      </c>
+      <c r="CB20">
+        <v>0</v>
+      </c>
+      <c r="CC20">
+        <v>0</v>
+      </c>
+      <c r="CD20">
+        <v>1</v>
+      </c>
+      <c r="CF20" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:85">
+      <c r="A21" s="6">
+        <v>1020</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>397</v>
+      </c>
+      <c r="D21" t="s">
+        <v>398</v>
+      </c>
+      <c r="E21">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s">
+        <v>358</v>
+      </c>
+      <c r="G21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" t="s">
+        <v>343</v>
+      </c>
+      <c r="J21" t="s">
+        <v>330</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>5</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>3</v>
+      </c>
+      <c r="AD21">
+        <v>3</v>
+      </c>
+      <c r="AE21">
+        <v>5</v>
+      </c>
+      <c r="AG21">
+        <v>5</v>
+      </c>
+      <c r="AI21">
+        <v>3</v>
+      </c>
+      <c r="AK21">
+        <v>3</v>
+      </c>
+      <c r="AM21">
+        <v>4</v>
+      </c>
+      <c r="AO21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>5</v>
+      </c>
+      <c r="AS21">
+        <v>4</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>1</v>
+      </c>
+      <c r="BK21">
+        <v>1</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>1</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>1</v>
+      </c>
+      <c r="CB21">
+        <v>1</v>
+      </c>
+      <c r="CC21">
+        <v>1</v>
+      </c>
+      <c r="CD21">
+        <v>1</v>
+      </c>
+      <c r="CF21" t="s">
+        <v>376</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>377</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
